--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -48074,6 +48074,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>19299</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="G2075" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -48097,6 +48097,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="G2076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -48120,6 +48120,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>9002</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>0.653999984264374</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>0.653999984264374</v>
+      </c>
+      <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -48143,6 +48143,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>9300</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>0.656000018119812</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -47984,22 +47984,22 @@
     </row>
     <row r="2071">
       <c r="A2071" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2071" t="n">
-        <v>128724</v>
+        <v>1000</v>
       </c>
       <c r="C2071" t="n">
-        <v>0.684000015258789</v>
+        <v>0.625999987125397</v>
       </c>
       <c r="D2071" t="n">
-        <v>0.629999995231628</v>
+        <v>0.625999987125397</v>
       </c>
       <c r="E2071" t="n">
-        <v>0.649999976158142</v>
+        <v>0.625999987125397</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.670000016689301</v>
+        <v>0.625999987125397</v>
       </c>
       <c r="G2071" t="s">
         <v>7</v>
@@ -48007,22 +48007,22 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2072" t="n">
-        <v>62148</v>
+        <v>128724</v>
       </c>
       <c r="C2072" t="n">
-        <v>0.698000013828278</v>
+        <v>0.684000015258789</v>
       </c>
       <c r="D2072" t="n">
-        <v>0.656000018119812</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="E2072" t="n">
-        <v>0.680000007152557</v>
+        <v>0.649999976158142</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.656000018119812</v>
+        <v>0.670000016689301</v>
       </c>
       <c r="G2072" t="s">
         <v>7</v>
@@ -48030,22 +48030,22 @@
     </row>
     <row r="2073">
       <c r="A2073" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2073" t="n">
-        <v>5000</v>
+        <v>62148</v>
       </c>
       <c r="C2073" t="n">
-        <v>0.663999974727631</v>
+        <v>0.698000013828278</v>
       </c>
       <c r="D2073" t="n">
-        <v>0.653999984264374</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="E2073" t="n">
+        <v>0.680000007152557</v>
+      </c>
+      <c r="F2073" t="n">
         <v>0.656000018119812</v>
-      </c>
-      <c r="F2073" t="n">
-        <v>0.653999984264374</v>
       </c>
       <c r="G2073" t="s">
         <v>7</v>
@@ -48053,22 +48053,22 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2074" t="n">
-        <v>26501</v>
+        <v>5000</v>
       </c>
       <c r="C2074" t="n">
-        <v>0.666000008583069</v>
+        <v>0.663999974727631</v>
       </c>
       <c r="D2074" t="n">
-        <v>0.656000018119812</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="E2074" t="n">
         <v>0.656000018119812</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.666000008583069</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="G2074" t="s">
         <v>7</v>
@@ -48076,13 +48076,13 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2075" t="n">
-        <v>19299</v>
+        <v>26501</v>
       </c>
       <c r="C2075" t="n">
-        <v>0.660000026226044</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="D2075" t="n">
         <v>0.656000018119812</v>
@@ -48091,7 +48091,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.656000018119812</v>
+        <v>0.666000008583069</v>
       </c>
       <c r="G2075" t="s">
         <v>7</v>
@@ -48099,13 +48099,13 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2076" t="n">
-        <v>3600</v>
+        <v>19299</v>
       </c>
       <c r="C2076" t="n">
-        <v>0.656000018119812</v>
+        <v>0.660000026226044</v>
       </c>
       <c r="D2076" t="n">
         <v>0.656000018119812</v>
@@ -48122,22 +48122,22 @@
     </row>
     <row r="2077">
       <c r="A2077" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2077" t="n">
-        <v>9002</v>
+        <v>3600</v>
       </c>
       <c r="C2077" t="n">
         <v>0.656000018119812</v>
       </c>
       <c r="D2077" t="n">
-        <v>0.653999984264374</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="E2077" t="n">
         <v>0.656000018119812</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.653999984264374</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="G2077" t="s">
         <v>7</v>
@@ -48145,24 +48145,47 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2078" t="n">
-        <v>9300</v>
+        <v>9002</v>
       </c>
       <c r="C2078" t="n">
-        <v>0.660000026226044</v>
+        <v>0.656000018119812</v>
       </c>
       <c r="D2078" t="n">
-        <v>0.656000018119812</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="E2078" t="n">
         <v>0.656000018119812</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.660000026226044</v>
+        <v>0.653999984264374</v>
       </c>
       <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>6378</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>0.667999982833862</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G2079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -54481,6 +54481,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G2082" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="H2082" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -54507,6 +54507,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="G2083" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="H2083" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -54533,6 +54533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>66686</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>0.657999992370605</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="H2084" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -54559,6 +54559,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>29159</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>0.666000008583069</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="H2085" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -54637,6 +54637,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>68194</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>0.662000000476837</v>
+      </c>
+      <c r="H2088" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MNL.MI.xlsx
+++ b/data/MNL.MI.xlsx
@@ -48458,7 +48458,9 @@
       <c r="E2091" t="n">
         <v>0.662000000476837</v>
       </c>
-      <c r="F2091"/>
+      <c r="F2091" t="n">
+        <v>0.660000026226044</v>
+      </c>
       <c r="G2091" t="s">
         <v>7</v>
       </c>
